--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:49</t>
+    <t xml:space="preserve">2026-09-24 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G17" s="2"/>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="G32" s="2"/>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="G33" s="2"/>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G49" s="2"/>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="G50" s="2"/>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="G51" s="2"/>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G66" s="2"/>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="G67" s="2"/>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="G68" s="2"/>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G83" s="2"/>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="G84" s="2"/>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G85" s="2"/>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G100" s="2"/>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="G101" s="2"/>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G102" s="2"/>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="G117" s="2"/>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="G118" s="2"/>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G119" s="2"/>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.21</v>
       </c>
       <c r="G134" s="2"/>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="G135" s="2"/>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="G136" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:38</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 20:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
